--- a/data_lake/industry/CFM/UFS.xlsx
+++ b/data_lake/industry/CFM/UFS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/CFM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB100BA-A3E4-42A2-8ADB-1B5B72FB46C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5C768B-A3FC-5247-8CFB-61A7E972B7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18140" yWindow="780" windowWidth="17860" windowHeight="20760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UFS 2.2 64GB" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -70,31 +70,31 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="180" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -132,50 +132,50 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -453,19 +453,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -488,7 +488,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -511,7 +511,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -534,7 +534,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -557,7 +557,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -580,7 +580,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -603,7 +603,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -626,7 +626,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -649,7 +649,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -672,7 +672,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -695,7 +695,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -718,7 +718,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -741,7 +741,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -764,7 +764,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -787,7 +787,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -810,7 +810,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -833,7 +833,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -856,7 +856,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -879,7 +879,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -902,7 +902,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -925,7 +925,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -948,7 +948,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -971,7 +971,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -994,7 +994,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -1040,7 +1040,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -1132,7 +1132,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -1201,7 +1201,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -1247,7 +1247,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -1362,7 +1362,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -1454,7 +1454,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -1500,7 +1500,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -1523,7 +1523,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -1592,7 +1592,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -1682,6 +1682,167 @@
       </c>
       <c r="G53" s="9">
         <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>26.3</v>
+      </c>
+      <c r="F54" s="9">
+        <v>28</v>
+      </c>
+      <c r="G54" s="9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>26.3</v>
+      </c>
+      <c r="F55" s="9">
+        <v>28</v>
+      </c>
+      <c r="G55" s="9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>24.3</v>
+      </c>
+      <c r="F56" s="9">
+        <v>26</v>
+      </c>
+      <c r="G56" s="9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>24.3</v>
+      </c>
+      <c r="F57" s="9">
+        <v>26</v>
+      </c>
+      <c r="G57" s="9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>24.3</v>
+      </c>
+      <c r="F58" s="9">
+        <v>26</v>
+      </c>
+      <c r="G58" s="9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>24.3</v>
+      </c>
+      <c r="F59" s="9">
+        <v>26</v>
+      </c>
+      <c r="G59" s="9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>24.3</v>
+      </c>
+      <c r="F60" s="9">
+        <v>26</v>
+      </c>
+      <c r="G60" s="9">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1692,19 +1853,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9244C5-F48F-43B7-9154-783F9DA9F8C6}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1727,7 +1888,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -1750,7 +1911,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -1773,7 +1934,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -1796,7 +1957,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -1819,7 +1980,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -1842,7 +2003,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -1865,7 +2026,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -1888,7 +2049,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -1911,7 +2072,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -1934,7 +2095,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -1957,7 +2118,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -1980,7 +2141,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -2003,7 +2164,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -2026,7 +2187,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -2049,7 +2210,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -2072,7 +2233,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -2095,7 +2256,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -2118,7 +2279,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -2141,7 +2302,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -2164,7 +2325,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -2187,7 +2348,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -2210,7 +2371,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -2233,7 +2394,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -2256,7 +2417,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -2279,7 +2440,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -2302,7 +2463,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -2325,7 +2486,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -2348,7 +2509,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -2371,7 +2532,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -2394,7 +2555,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -2417,7 +2578,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -2440,7 +2601,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -2463,7 +2624,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -2486,7 +2647,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -2509,7 +2670,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -2532,7 +2693,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -2555,7 +2716,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -2578,7 +2739,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -2601,7 +2762,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -2624,7 +2785,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -2647,7 +2808,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -2670,7 +2831,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -2693,7 +2854,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -2716,7 +2877,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -2739,7 +2900,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -2762,7 +2923,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -2785,7 +2946,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -2808,7 +2969,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -2831,7 +2992,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -2854,7 +3015,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -2877,7 +3038,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -2900,7 +3061,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -2920,6 +3081,167 @@
         <v>35.5</v>
       </c>
       <c r="G53" s="12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="12">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F54" s="12">
+        <v>35.5</v>
+      </c>
+      <c r="G54" s="12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="12">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F55" s="12">
+        <v>35.5</v>
+      </c>
+      <c r="G55" s="12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="12">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F56" s="12">
+        <v>35.5</v>
+      </c>
+      <c r="G56" s="12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="12">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F57" s="12">
+        <v>35.5</v>
+      </c>
+      <c r="G57" s="12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="12">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F58" s="12">
+        <v>35.5</v>
+      </c>
+      <c r="G58" s="12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="12">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F59" s="12">
+        <v>35.5</v>
+      </c>
+      <c r="G59" s="12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="12">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F60" s="12">
+        <v>35.5</v>
+      </c>
+      <c r="G60" s="12">
         <v>33</v>
       </c>
     </row>
@@ -2931,19 +3253,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6478684B-CAE8-48EE-80F6-6A07A9D856F1}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2966,7 +3288,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -2989,7 +3311,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -3012,7 +3334,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -3035,7 +3357,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -3058,7 +3380,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -3081,7 +3403,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -3104,7 +3426,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -3127,7 +3449,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -3150,7 +3472,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -3173,7 +3495,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -3196,7 +3518,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -3219,7 +3541,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -3242,7 +3564,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -3265,7 +3587,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -3288,7 +3610,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -3311,7 +3633,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -3334,7 +3656,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -3357,7 +3679,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -3380,7 +3702,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -3403,7 +3725,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -3426,7 +3748,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -3449,7 +3771,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -3472,7 +3794,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -3495,7 +3817,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -3518,7 +3840,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -3541,7 +3863,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -3564,7 +3886,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -3587,7 +3909,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -3610,7 +3932,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -3633,7 +3955,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -3656,7 +3978,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -3679,7 +4001,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -3702,7 +4024,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -3725,7 +4047,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -3748,7 +4070,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -3771,7 +4093,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -3794,7 +4116,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -3817,7 +4139,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -3840,7 +4162,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -3863,7 +4185,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -3886,7 +4208,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -3909,7 +4231,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -3932,7 +4254,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -3955,7 +4277,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -3978,7 +4300,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -4001,7 +4323,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -4024,7 +4346,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -4047,7 +4369,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -4070,7 +4392,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -4093,7 +4415,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -4116,7 +4438,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -4139,7 +4461,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -4159,6 +4481,167 @@
         <v>63</v>
       </c>
       <c r="G53" s="9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>58.7</v>
+      </c>
+      <c r="F54" s="9">
+        <v>63</v>
+      </c>
+      <c r="G54" s="9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>58.7</v>
+      </c>
+      <c r="F55" s="9">
+        <v>63</v>
+      </c>
+      <c r="G55" s="9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>58.7</v>
+      </c>
+      <c r="F56" s="9">
+        <v>63</v>
+      </c>
+      <c r="G56" s="9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>58.7</v>
+      </c>
+      <c r="F57" s="9">
+        <v>63</v>
+      </c>
+      <c r="G57" s="9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>58.7</v>
+      </c>
+      <c r="F58" s="9">
+        <v>63</v>
+      </c>
+      <c r="G58" s="9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>58.7</v>
+      </c>
+      <c r="F59" s="9">
+        <v>63</v>
+      </c>
+      <c r="G59" s="9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>58.7</v>
+      </c>
+      <c r="F60" s="9">
+        <v>63</v>
+      </c>
+      <c r="G60" s="9">
         <v>60</v>
       </c>
     </row>
@@ -4170,19 +4653,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9291558D-A342-4E30-81D9-3EB746F72AE7}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4205,7 +4688,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -4228,7 +4711,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -4251,7 +4734,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -4274,7 +4757,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -4297,7 +4780,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -4320,7 +4803,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -4343,7 +4826,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -4366,7 +4849,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -4389,7 +4872,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -4412,7 +4895,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -4435,7 +4918,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -4458,7 +4941,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -4481,7 +4964,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -4504,7 +4987,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -4527,7 +5010,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -4550,7 +5033,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -4573,7 +5056,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -4596,7 +5079,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -4619,7 +5102,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -4642,7 +5125,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -4665,7 +5148,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -4688,7 +5171,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -4711,7 +5194,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -4734,7 +5217,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -4757,7 +5240,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -4780,7 +5263,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -4803,7 +5286,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -4826,7 +5309,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -4849,7 +5332,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -4872,7 +5355,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -4895,7 +5378,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -4918,7 +5401,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -4941,7 +5424,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -4964,7 +5447,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -4987,7 +5470,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -5010,7 +5493,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -5033,7 +5516,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -5056,7 +5539,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -5079,7 +5562,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -5102,7 +5585,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -5125,7 +5608,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -5148,7 +5631,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -5171,7 +5654,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -5194,7 +5677,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -5217,7 +5700,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -5240,7 +5723,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -5263,7 +5746,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -5286,7 +5769,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -5309,7 +5792,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -5332,7 +5815,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -5355,7 +5838,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -5378,7 +5861,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -5398,6 +5881,167 @@
         <v>93</v>
       </c>
       <c r="G53" s="9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>89.5</v>
+      </c>
+      <c r="F54" s="9">
+        <v>93</v>
+      </c>
+      <c r="G54" s="9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>89.5</v>
+      </c>
+      <c r="F55" s="9">
+        <v>93</v>
+      </c>
+      <c r="G55" s="9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>89.5</v>
+      </c>
+      <c r="F56" s="9">
+        <v>93</v>
+      </c>
+      <c r="G56" s="9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>89.5</v>
+      </c>
+      <c r="F57" s="9">
+        <v>93</v>
+      </c>
+      <c r="G57" s="9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>89.5</v>
+      </c>
+      <c r="F58" s="9">
+        <v>93</v>
+      </c>
+      <c r="G58" s="9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>89.5</v>
+      </c>
+      <c r="F59" s="9">
+        <v>93</v>
+      </c>
+      <c r="G59" s="9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>89.5</v>
+      </c>
+      <c r="F60" s="9">
+        <v>93</v>
+      </c>
+      <c r="G60" s="9">
         <v>90</v>
       </c>
     </row>
